--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.13454459508074</v>
+        <v>11.88436349670062</v>
       </c>
       <c r="D2" t="n">
-        <v>71.44349480585559</v>
+        <v>11.60956790595153</v>
       </c>
       <c r="E2" t="n">
-        <v>7.278813047620805</v>
+        <v>1.182807120238381</v>
       </c>
       <c r="F2" t="n">
-        <v>17.18297526942391</v>
+        <v>2.792233481281385</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.57691849983913</v>
+        <v>9.51874925622386</v>
       </c>
       <c r="D3" t="n">
-        <v>37.07754426700778</v>
+        <v>6.025100943388765</v>
       </c>
       <c r="E3" t="n">
-        <v>7.278813047620805</v>
+        <v>1.182807120238381</v>
       </c>
       <c r="F3" t="n">
-        <v>17.18297526942391</v>
+        <v>2.792233481281385</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
